--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G483"/>
+  <dimension ref="A1:G487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13477,6 +13477,114 @@
       <c r="G483" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="C484" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="D484" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="E484" t="n">
+        <v>355.04</v>
+      </c>
+      <c r="F484" t="n">
+        <v>352.93</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>368.03</v>
+      </c>
+      <c r="C485" t="n">
+        <v>359.25</v>
+      </c>
+      <c r="D485" t="n">
+        <v>356.9</v>
+      </c>
+      <c r="E485" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="F485" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>367.93</v>
+      </c>
+      <c r="C486" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="D486" t="n">
+        <v>356.32</v>
+      </c>
+      <c r="E486" t="n">
+        <v>354.21</v>
+      </c>
+      <c r="F486" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="C487" t="n">
+        <v>358.09</v>
+      </c>
+      <c r="D487" t="n">
+        <v>355.27</v>
+      </c>
+      <c r="E487" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="F487" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18664,6 +18772,56 @@
       </c>
       <c r="B517" t="n">
         <v>-1.06</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -18832,28 +18990,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.812296014794136</v>
+        <v>2.796039195625035</v>
       </c>
       <c r="J2" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K2" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.830546948744358</v>
+        <v>0.8304635758942494</v>
       </c>
       <c r="M2" t="n">
-        <v>7.983440894828128</v>
+        <v>7.995269128886862</v>
       </c>
       <c r="N2" t="n">
-        <v>92.38624544494515</v>
+        <v>92.41039154187924</v>
       </c>
       <c r="O2" t="n">
-        <v>9.611776393827789</v>
+        <v>9.613032380153477</v>
       </c>
       <c r="P2" t="n">
-        <v>302.3055009725041</v>
+        <v>302.472933294693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18910,28 +19068,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.944721612592645</v>
+        <v>2.915036410164236</v>
       </c>
       <c r="J3" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K3" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8123443449139123</v>
+        <v>0.8087689111045981</v>
       </c>
       <c r="M3" t="n">
-        <v>8.783495397655093</v>
+        <v>8.852908711958179</v>
       </c>
       <c r="N3" t="n">
-        <v>114.6859011539428</v>
+        <v>116.3359356195447</v>
       </c>
       <c r="O3" t="n">
-        <v>10.70915034696697</v>
+        <v>10.78591375913718</v>
       </c>
       <c r="P3" t="n">
-        <v>297.8848714664997</v>
+        <v>298.1905889503885</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18988,28 +19146,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.928884488989686</v>
+        <v>2.899461206640785</v>
       </c>
       <c r="J4" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8355559451589272</v>
+        <v>0.8318146225404478</v>
       </c>
       <c r="M4" t="n">
-        <v>8.015508200545113</v>
+        <v>8.098615582516505</v>
       </c>
       <c r="N4" t="n">
-        <v>96.83578344629112</v>
+        <v>98.59694865620421</v>
       </c>
       <c r="O4" t="n">
-        <v>9.840517437934405</v>
+        <v>9.929599622150141</v>
       </c>
       <c r="P4" t="n">
-        <v>295.7710297638501</v>
+        <v>296.0738888203649</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19066,28 +19224,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.658865529965595</v>
+        <v>2.632628436340906</v>
       </c>
       <c r="J5" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K5" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L5" t="n">
-        <v>0.831954414880138</v>
+        <v>0.8284329707009502</v>
       </c>
       <c r="M5" t="n">
-        <v>7.384710839625759</v>
+        <v>7.460830823673349</v>
       </c>
       <c r="N5" t="n">
-        <v>81.75613887820356</v>
+        <v>83.10888635700869</v>
       </c>
       <c r="O5" t="n">
-        <v>9.041910134379989</v>
+        <v>9.116407535702246</v>
       </c>
       <c r="P5" t="n">
-        <v>298.6949788367268</v>
+        <v>298.9651819859377</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19144,28 +19302,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.789637148192516</v>
+        <v>1.769581811000695</v>
       </c>
       <c r="J6" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="K6" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7486506612466015</v>
+        <v>0.7444509685933628</v>
       </c>
       <c r="M6" t="n">
-        <v>6.437168004133663</v>
+        <v>6.480195440666686</v>
       </c>
       <c r="N6" t="n">
-        <v>61.56424462691404</v>
+        <v>62.24024615822189</v>
       </c>
       <c r="O6" t="n">
-        <v>7.846288589321325</v>
+        <v>7.889248770207585</v>
       </c>
       <c r="P6" t="n">
-        <v>316.3237882322185</v>
+        <v>316.5303279091191</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19203,7 +19361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G483"/>
+  <dimension ref="A1:G487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37073,6 +37231,154 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>-46.29369969202741,169.92598596133405</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>-46.29427219884642,169.92562705218626</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>-46.294864035156166,169.92535743238054</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-46.29545200290531,169.92506997837953</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>-46.296043450514325,169.924798623584</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>-46.293695481539665,169.92596651819048</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>-46.29426906105629,169.92561256257835</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>-46.29485987821813,169.92533823655847</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-46.29545146652133,169.92506750147518</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-46.29604194862587,169.92479168818411</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-46.293695213355626,169.9259652797738</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-46.294267612844855,169.9256058750676</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-46.294858322717914,169.92533105360647</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-46.29544977691146,169.92505969922686</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-46.29604168043146,169.92479044971992</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-46.293692397422404,169.9259522763994</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-46.29426595008312,169.92559819681495</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-46.29485550672503,169.9253180499876</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-46.29544712180919,169.92504743855196</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-46.29604012490363,169.9247832666277</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G487"/>
+  <dimension ref="A1:G488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13585,6 +13585,33 @@
       <c r="G487" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>365.04</v>
+      </c>
+      <c r="C488" t="n">
+        <v>355.71</v>
+      </c>
+      <c r="D488" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="E488" t="n">
+        <v>350.88</v>
+      </c>
+      <c r="F488" t="n">
+        <v>349.35</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B522"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18822,6 +18849,16 @@
       </c>
       <c r="B522" t="n">
         <v>0.12</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-0.27</v>
       </c>
     </row>
   </sheetData>
@@ -18990,28 +19027,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.796039195625035</v>
+        <v>2.790753628697379</v>
       </c>
       <c r="J2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8304635758942494</v>
+        <v>0.830098934906918</v>
       </c>
       <c r="M2" t="n">
-        <v>7.995269128886862</v>
+        <v>8.004020213430696</v>
       </c>
       <c r="N2" t="n">
-        <v>92.41039154187924</v>
+        <v>92.55594495875809</v>
       </c>
       <c r="O2" t="n">
-        <v>9.613032380153477</v>
+        <v>9.620600031118542</v>
       </c>
       <c r="P2" t="n">
-        <v>302.472933294693</v>
+        <v>302.5275080701342</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19068,28 +19105,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.915036410164236</v>
+        <v>2.906349029205425</v>
       </c>
       <c r="J3" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K3" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8087689111045981</v>
+        <v>0.8073862698959737</v>
       </c>
       <c r="M3" t="n">
-        <v>8.852908711958179</v>
+        <v>8.876794722972265</v>
       </c>
       <c r="N3" t="n">
-        <v>116.3359356195447</v>
+        <v>117.0028651813957</v>
       </c>
       <c r="O3" t="n">
-        <v>10.78591375913718</v>
+        <v>10.816786268638</v>
       </c>
       <c r="P3" t="n">
-        <v>298.1905889503885</v>
+        <v>298.2802882904004</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19146,28 +19183,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.899461206640785</v>
+        <v>2.890538594748153</v>
       </c>
       <c r="J4" t="n">
+        <v>487</v>
+      </c>
+      <c r="K4" t="n">
         <v>486</v>
       </c>
-      <c r="K4" t="n">
-        <v>485</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.8318146225404478</v>
+        <v>0.8302658898590608</v>
       </c>
       <c r="M4" t="n">
-        <v>8.098615582516505</v>
+        <v>8.127787144069499</v>
       </c>
       <c r="N4" t="n">
-        <v>98.59694865620421</v>
+        <v>99.35198481175999</v>
       </c>
       <c r="O4" t="n">
-        <v>9.929599622150141</v>
+        <v>9.967546579362446</v>
       </c>
       <c r="P4" t="n">
-        <v>296.0738888203649</v>
+        <v>296.1659672855396</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19224,28 +19261,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.632628436340906</v>
+        <v>2.624769496859272</v>
       </c>
       <c r="J5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8284329707009502</v>
+        <v>0.826999611791402</v>
       </c>
       <c r="M5" t="n">
-        <v>7.460830823673349</v>
+        <v>7.48662637494957</v>
       </c>
       <c r="N5" t="n">
-        <v>83.10888635700869</v>
+        <v>83.6795220193131</v>
       </c>
       <c r="O5" t="n">
-        <v>9.116407535702246</v>
+        <v>9.147651174990939</v>
       </c>
       <c r="P5" t="n">
-        <v>298.9651819859377</v>
+        <v>299.0463274644241</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19302,28 +19339,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.769581811000695</v>
+        <v>1.763442838578105</v>
       </c>
       <c r="J6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7444509685933628</v>
+        <v>0.7426623185155536</v>
       </c>
       <c r="M6" t="n">
-        <v>6.480195440666686</v>
+        <v>6.496238397232807</v>
       </c>
       <c r="N6" t="n">
-        <v>62.24024615822189</v>
+        <v>62.56476912677405</v>
       </c>
       <c r="O6" t="n">
-        <v>7.889248770207585</v>
+        <v>7.90978944895337</v>
       </c>
       <c r="P6" t="n">
-        <v>316.5303279091191</v>
+        <v>316.5937143056947</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19361,7 +19398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G487"/>
+  <dimension ref="A1:G488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37379,6 +37416,43 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.29368746283114,169.9259294895372</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.29425956721882,169.92556872223682</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.294848346050884,169.92528498364868</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.295440846107766,169.92501845877982</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-46.296033849148884,169.9247542865704</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0525/nzd0525.xlsx
+++ b/data/nzd0525/nzd0525.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13612,6 +13612,60 @@
       <c r="G488" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="C489" t="n">
+        <v>355.78</v>
+      </c>
+      <c r="D489" t="n">
+        <v>352.51</v>
+      </c>
+      <c r="E489" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="F489" t="n">
+        <v>348.77</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>363.24</v>
+      </c>
+      <c r="C490" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="D490" t="n">
+        <v>351.48</v>
+      </c>
+      <c r="E490" t="n">
+        <v>349.14</v>
+      </c>
+      <c r="F490" t="n">
+        <v>347.62</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18859,6 +18913,26 @@
       </c>
       <c r="B523" t="n">
         <v>-0.27</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -19027,28 +19101,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.790753628697379</v>
+        <v>2.779153352555904</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.830098934906918</v>
+        <v>0.8290595472777627</v>
       </c>
       <c r="M2" t="n">
-        <v>8.004020213430696</v>
+        <v>8.026223252405233</v>
       </c>
       <c r="N2" t="n">
-        <v>92.55594495875809</v>
+        <v>92.98530548508496</v>
       </c>
       <c r="O2" t="n">
-        <v>9.620600031118542</v>
+        <v>9.642888855788236</v>
       </c>
       <c r="P2" t="n">
-        <v>302.5275080701342</v>
+        <v>302.6478345975387</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19105,28 +19179,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.906349029205425</v>
+        <v>2.888575548062226</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8073862698959737</v>
+        <v>0.8044658856772242</v>
       </c>
       <c r="M3" t="n">
-        <v>8.876794722972265</v>
+        <v>8.927573557393663</v>
       </c>
       <c r="N3" t="n">
-        <v>117.0028651813957</v>
+        <v>118.4165875543396</v>
       </c>
       <c r="O3" t="n">
-        <v>10.816786268638</v>
+        <v>10.88193859357512</v>
       </c>
       <c r="P3" t="n">
-        <v>298.2802882904004</v>
+        <v>298.4646425439842</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19183,28 +19257,28 @@
         <v>0.196</v>
       </c>
       <c r="I4" t="n">
-        <v>2.890538594748153</v>
+        <v>2.872134753161697</v>
       </c>
       <c r="J4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K4" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8302658898590608</v>
+        <v>0.8269392129107801</v>
       </c>
       <c r="M4" t="n">
-        <v>8.127787144069499</v>
+        <v>8.189867762715302</v>
       </c>
       <c r="N4" t="n">
-        <v>99.35198481175999</v>
+        <v>100.9788095991754</v>
       </c>
       <c r="O4" t="n">
-        <v>9.967546579362446</v>
+        <v>10.04882130397269</v>
       </c>
       <c r="P4" t="n">
-        <v>296.1659672855396</v>
+        <v>296.3567600409439</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19261,28 +19335,28 @@
         <v>0.199</v>
       </c>
       <c r="I5" t="n">
-        <v>2.624769496859272</v>
+        <v>2.607999672814871</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.826999611791402</v>
+        <v>0.8236651469569137</v>
       </c>
       <c r="M5" t="n">
-        <v>7.48662637494957</v>
+        <v>7.545508876861074</v>
       </c>
       <c r="N5" t="n">
-        <v>83.6795220193131</v>
+        <v>85.022272750238</v>
       </c>
       <c r="O5" t="n">
-        <v>9.147651174990939</v>
+        <v>9.220752287651914</v>
       </c>
       <c r="P5" t="n">
-        <v>299.0463274644241</v>
+        <v>299.2202721478283</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19339,28 +19413,28 @@
         <v>0.1438</v>
       </c>
       <c r="I6" t="n">
-        <v>1.763442838578105</v>
+        <v>1.750193321265578</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7426623185155536</v>
+        <v>0.7384107264651869</v>
       </c>
       <c r="M6" t="n">
-        <v>6.496238397232807</v>
+        <v>6.532750594055026</v>
       </c>
       <c r="N6" t="n">
-        <v>62.56476912677405</v>
+        <v>63.36131083643704</v>
       </c>
       <c r="O6" t="n">
-        <v>7.90978944895337</v>
+        <v>7.95998183643889</v>
       </c>
       <c r="P6" t="n">
-        <v>316.5937143056947</v>
+        <v>316.731145841803</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19398,7 +19472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G488"/>
+  <dimension ref="A1:G490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37453,6 +37527,80 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.293686443730216,169.92592478355533</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.29425975495022,169.92556958913607</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.294848104679694,169.92528386905317</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.29543907603683,169.9250102849992</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.296032293618815,169.9247471034803</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.293682635509306,169.92590719804576</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.29425723398505,169.925557947918</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.29484534231962,169.92527111312722</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.295436179555885,169.92499690972298</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.29602920937686,169.92473286114785</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
